--- a/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-lufu-lnc-kco.xlsx
+++ b/branches/release/v2027.0.0-ballot/ValueSet-mii-vs-lufu-lnc-kco.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02</t>
+    <t>2026-09-15</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -93,7 +93,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>This value set includes content from SNOMED CT, which is copyright © 2002+ International Health Terminology Standards Development Organisation (IHTSDO), and distributed by agreement between IHTSDO and HL7. Implementer use of SNOMED CT is not covered by this agreement</t>
+    <t>This material contains content from LOINC (http://loinc.org). LOINC is copyright © 1995-2020, Regenstrief Institute, Inc. and the Logical Observation Identifiers Names and Codes (LOINC) Committee and is available at no cost under the license at http://loinc.org/license. LOINC® is a registered United States trademark of Regenstrief Institute, Inc)</t>
   </si>
   <si>
     <t>Immutable</t>
